--- a/src/test/resources/TEST_DATA/SettingsPageData.xlsx
+++ b/src/test/resources/TEST_DATA/SettingsPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="51"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" state="visible" r:id="rId1"/>
@@ -687,10 +687,10 @@
     <t>mohanw</t>
   </si>
   <si>
+    <t>Hoax@2346</t>
+  </si>
+  <si>
     <t>newPassword</t>
-  </si>
-  <si>
-    <t>Hoax@2345</t>
   </si>
   <si>
     <t>primaryAccountSentSuccessMsg</t>
@@ -1430,6 +1430,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1466,7 +1469,6 @@
     <xf fontId="3" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2446,6 +2448,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="12.57421875"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -2462,8 +2467,8 @@
       <c r="A2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+      <c r="B2" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -2490,15 +2495,15 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="15" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2539,6 +2544,8 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="15.57421875"/>
+    <col customWidth="1" min="2" max="2" width="12.57421875"/>
+    <col customWidth="1" min="3" max="3" width="12.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2549,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>210</v>
@@ -2562,11 +2569,11 @@
       <c r="A2" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>211</v>
@@ -2795,16 +2802,16 @@
       <c r="G2" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>232</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="17">
         <v>0</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="17" t="s">
         <v>233</v>
       </c>
     </row>
@@ -2916,7 +2923,7 @@
       <c r="D2" t="s">
         <v>233</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>230</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -2958,10 +2965,10 @@
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1" ht="57">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -2985,7 +2992,7 @@
       <c r="I1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>254</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3020,64 +3027,64 @@
       </c>
     </row>
     <row r="2" s="4" customFormat="1" ht="114">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="17">
         <v>30001</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="17">
         <v>501</v>
       </c>
-      <c r="R2" s="16">
+      <c r="R2" s="17">
         <v>0</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="T2" s="17" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3201,7 +3208,7 @@
       <c r="C2" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>280</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -3321,7 +3328,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>271</v>
       </c>
       <c r="B1" t="s">
@@ -3499,7 +3506,7 @@
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>286</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3534,7 +3541,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>271</v>
       </c>
       <c r="B1" t="s">
@@ -3775,7 +3782,7 @@
       <c r="A2" t="s">
         <v>323</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>300</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -3888,7 +3895,7 @@
       <c r="G2" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>341</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -4083,10 +4090,10 @@
       <c r="B3" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>356</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -4127,7 +4134,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>364</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -4187,7 +4194,7 @@
       <c r="A1" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>364</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -4309,7 +4316,7 @@
       <c r="G2" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="27" t="s">
         <v>392</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -4335,7 +4342,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -5517,7 +5524,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5538,7 +5545,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -5629,7 +5636,7 @@
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -5652,7 +5659,7 @@
       <c r="D2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="5" t="s">
         <v>410</v>
       </c>
       <c r="F2" s="5" t="s">

--- a/src/test/resources/TEST_DATA/SettingsPageData.xlsx
+++ b/src/test/resources/TEST_DATA/SettingsPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="SettingsPanelUserData" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>settingsUserDetails</t>
   </si>
@@ -40,18 +40,15 @@
     <t>password</t>
   </si>
   <si>
-    <t>safras77</t>
-  </si>
-  <si>
-    <t>Abcd@1234</t>
+    <t>123sampath</t>
+  </si>
+  <si>
+    <t>Hoax@1234</t>
   </si>
   <si>
     <t>newPassword</t>
   </si>
   <si>
-    <t>Hoax@1234</t>
-  </si>
-  <si>
     <t>Hoax@5456</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
   </si>
   <si>
     <t>passwordForRevertThree</t>
-  </si>
-  <si>
-    <t>123sampath</t>
   </si>
   <si>
     <t xml:space="preserve">LOGIN FAILED! PLEASE RECHECK THE USERNAME AND PASSWORD AND TRY AGAIN. REMAINING LOGIN ATTEMPTS: 4</t>
@@ -108,10 +102,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -641,7 +638,7 @@
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -685,24 +682,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -723,19 +720,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -763,46 +760,46 @@
       <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
